--- a/imperium-api/test_arq_output.xlsx
+++ b/imperium-api/test_arq_output.xlsx
@@ -85,7 +85,7 @@
     <t>Audit Trail Hash (Pricing Integrity Key):</t>
   </si>
   <si>
-    <t>b37617808a37e3d603a9e20bf9becce05b5c791f40493ebfbccc38d39ae2a6e8</t>
+    <t>dc035e74c087ee6dab08ae2149f40914da1e235ed9d1f24e0fb53265fc9ea7e1</t>
   </si>
 </sst>
 </file>

--- a/imperium-api/test_arq_output.xlsx
+++ b/imperium-api/test_arq_output.xlsx
@@ -85,7 +85,7 @@
     <t>Audit Trail Hash (Pricing Integrity Key):</t>
   </si>
   <si>
-    <t>dc035e74c087ee6dab08ae2149f40914da1e235ed9d1f24e0fb53265fc9ea7e1</t>
+    <t>0b90324c1bc3e5d83a5dc48c6a606ba85c4c3b6e7d47f53fc05c26a88fa1c3f7</t>
   </si>
 </sst>
 </file>
